--- a/data/raw/260601_SEC양산평가.xlsx
+++ b/data/raw/260601_SEC양산평가.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -572,24 +572,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>연속 적재 정밀도 점검</t>
+          <t>사이클 반복 안정성 검증</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>비전 파라미터 튜닝</t>
+          <t>연속 적재 정밀도 점검</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -609,14 +609,14 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -626,24 +626,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>노출 보정 후 재검증</t>
+          <t>비전 파라미터 튜닝</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -653,28 +653,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>그리퍼 압력 캘리브레이션</t>
+          <t>노출 보정 후 재검증</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
         <v>14</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>ERR-002 발생 → 연속 리셋</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -684,24 +680,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>표면 검사 단계 검증</t>
+          <t>그리퍼 압력 캘리브레이션</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ERR-002 발생 → 연속 리셋</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -711,28 +711,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>경로 플래너 검증</t>
+          <t>그리퍼 압력 캘리브레이션</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>ERR-003 발생 → 연속 리셋</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -742,24 +738,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>역광 조건 재현 시험</t>
+          <t>표면 검사 단계 검증</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -769,28 +765,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>차광 설치 후 재검증</t>
+          <t>경로 플래너 검증</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ERR-001 발생 → 연속 리셋</t>
+          <t>ERR-003 발생 → 연속 리셋</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -800,24 +796,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>연속 운전 안정성</t>
+          <t>경로 플래너 검증</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -827,28 +823,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>후속 로트 그립 검증</t>
+          <t>역광 조건 재현 시험</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
         <v>16</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>ERR-002 발생 → 연속 리셋</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -858,28 +850,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>센서 노이즈 점검</t>
+          <t>차광 설치 후 재검증</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ERR-005 발생 → 연속 리셋</t>
+          <t>ERR-001 발생 → 연속 리셋</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -889,28 +881,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>그리퍼 패드 점검</t>
+          <t>차광 설치 후 재검증</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>ERR-002 발생 → 연속 리셋</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -920,7 +908,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>안정화 연속 운전</t>
+          <t>연속 운전 안정성</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -930,14 +918,14 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -947,24 +935,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>무고장 연속 운전</t>
+          <t>후속 로트 그립 검증</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ERR-002 발생 → 연속 리셋</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -974,24 +966,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>무고장 연속 운전</t>
+          <t>후속 로트 그립 검증</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1001,24 +993,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>무고장 연속 운전</t>
+          <t>센서 노이즈 점검</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>ERR-005 발생 → 연속 리셋</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1028,24 +1024,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>무고장 연속 운전</t>
+          <t>센서 노이즈 점검</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1055,24 +1051,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>무고장 연속 운전</t>
+          <t>그리퍼 패드 점검</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>ERR-002 발생 → 연속 리셋</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1082,24 +1082,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>장기 신뢰성 입증</t>
+          <t>그리퍼 패드 점검</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1109,24 +1109,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>장기 신뢰성 입증</t>
+          <t>안정화 연속 운전</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>장기 신뢰성 입증</t>
+          <t>무고장 연속 운전</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1146,14 +1146,14 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1163,46 +1163,235 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>장기 신뢰성 입증</t>
+          <t>무고장 연속 운전</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>홍길동, 김철수</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>무고장 연속 운전</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>홍길동, 김철수</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>무고장 연속 운전</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>홍길동, 김철수</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>무고장 연속 운전</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>홍길동, 김철수</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>장기 신뢰성 입증</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>홍길동, 김철수</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>장기 신뢰성 입증</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>홍길동, 김철수</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>장기 신뢰성 입증</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>홍길동, 김철수</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>장기 신뢰성 입증</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>홍길동, 김철수</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>홍길동, 김철수</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>장기 신뢰성 입증</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D33" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>168</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
